--- a/Pasta1.xlsx
+++ b/Pasta1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anderson\PycharmProjects\robo_boby\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FDD57C6-675C-4779-9041-CA7E1507C7CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{756D76DC-62F2-4D0E-B707-954DA83994C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{196EC739-9E9B-48A5-AB5F-83FDC26EF1CB}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
   <si>
     <t>Código</t>
   </si>
@@ -39,73 +39,25 @@
     <t>UN</t>
   </si>
   <si>
-    <t>CONJUNTO CANHAO 1300</t>
-  </si>
-  <si>
-    <t>TAMPA HASTE ASA</t>
-  </si>
-  <si>
-    <t>CONJUNTO PUXADOR CORTE</t>
-  </si>
-  <si>
-    <t>CONJUNTO PL PUXADOR MAIOR</t>
-  </si>
-  <si>
-    <t>CONJUNTO PL PUXADOR MENOR</t>
-  </si>
-  <si>
-    <t>CONJUNTO CAIXA COMANDO</t>
-  </si>
-  <si>
-    <t>ALAVANCA MOVIMENTO</t>
-  </si>
-  <si>
-    <t>EIXO MANCAL MOVIMENTO</t>
-  </si>
-  <si>
-    <t>MANCAL MOVIMENTADOR</t>
-  </si>
-  <si>
-    <t>LUVA REGISTRO</t>
-  </si>
-  <si>
-    <t>HASTE MENOR QUADRO INFLADOR</t>
-  </si>
-  <si>
-    <t>HASTE CENTRAL QUADRO INFLADOR</t>
-  </si>
-  <si>
-    <t>DISTANCIADOR BASE ASA V2</t>
-  </si>
-  <si>
-    <t>PROLONGADOR MOVEL LATERAL</t>
-  </si>
-  <si>
-    <t>HASTE QUADRO MAIOR INFLADOR</t>
-  </si>
-  <si>
-    <t>BASE SUPORTE INFLADORES</t>
-  </si>
-  <si>
-    <t>HASTE MAIOR BASE TRILHO</t>
-  </si>
-  <si>
-    <t>HASTE MENOR BASE TRILHO</t>
-  </si>
-  <si>
-    <t>HASTE CENTRAL BASE TRILHO</t>
-  </si>
-  <si>
-    <t>ARRUELA DISTANCIADORA MPG32</t>
-  </si>
-  <si>
-    <t>PORCA PARAFUSO REGULAGEM</t>
-  </si>
-  <si>
-    <t>SUBCONJUNTO CONECTOR EXT.</t>
-  </si>
-  <si>
-    <t>SUBCONJUNTO INTERNO EXT. V2</t>
+    <t>CONJUNTO ASA GAIVOTA PNEU</t>
+  </si>
+  <si>
+    <t>CONJUNTO CONTROLE TENSAO DIG</t>
+  </si>
+  <si>
+    <t>CONJUNTO QUADRO F INFLADOR</t>
+  </si>
+  <si>
+    <t>CONJUNTO BASE TRILHO INFLADOR</t>
+  </si>
+  <si>
+    <t>CONJUNTO MESA SOLDA BASIC 2000</t>
+  </si>
+  <si>
+    <t>EIXO CILINDRO SOLDA</t>
+  </si>
+  <si>
+    <t>CONJUNTO CONE REGULADOR</t>
   </si>
 </sst>
 </file>
@@ -457,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A19B4867-D6B9-4378-B826-8F7201F8AF0D}">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -478,7 +430,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>21832</v>
+        <v>22207</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
@@ -489,7 +441,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>22005</v>
+        <v>22257</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -500,7 +452,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>22117</v>
+        <v>22275</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
@@ -511,7 +463,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>22123</v>
+        <v>22276</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
@@ -522,7 +474,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>22124</v>
+        <v>22300</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
@@ -533,7 +485,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>22235</v>
+        <v>22311</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
@@ -544,188 +496,12 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>22252</v>
+        <v>15087</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>22254</v>
-      </c>
-      <c r="B9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>22255</v>
-      </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>22258</v>
-      </c>
-      <c r="B11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>22273</v>
-      </c>
-      <c r="B12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>22274</v>
-      </c>
-      <c r="B13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>22277</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>22278</v>
-      </c>
-      <c r="B15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>22279</v>
-      </c>
-      <c r="B16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>22281</v>
-      </c>
-      <c r="B17" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>22282</v>
-      </c>
-      <c r="B18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>22284</v>
-      </c>
-      <c r="B19" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>22286</v>
-      </c>
-      <c r="B20" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>22294</v>
-      </c>
-      <c r="B21" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>18363</v>
-      </c>
-      <c r="B22" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>19504</v>
-      </c>
-      <c r="B23" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>20140</v>
-      </c>
-      <c r="B24" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" t="s">
         <v>3</v>
       </c>
     </row>
